--- a/test-fixtures/xlsx/sheets-many.xlsx
+++ b/test-fixtures/xlsx/sheets-many.xlsx
@@ -407,7 +407,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -429,7 +429,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -451,7 +451,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -473,7 +473,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -495,7 +495,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -517,7 +517,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -539,7 +539,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -561,7 +561,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -583,7 +583,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -605,6 +605,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>